--- a/docs/02b-人工耗时-组员6.xlsx
+++ b/docs/02b-人工耗时-组员6.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -474,7 +474,7 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="62" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -540,7 +540,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>BubbleSort</t>
+          <t>LinearSearch</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -560,11 +560,11 @@
         <v>6</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>包级类，测试同包实例化；泛型排序，测了 Integer 与 String</t>
+          <t>补位（组员5 未写）：类为 public；null 数组 / 空数组 / null 关键字都返回 -1，数组里的 null 元素跳过</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>SortedLinkedList</t>
+          <t>ReverseString</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -591,14 +591,14 @@
       </c>
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>有序链表；insert/delete/search/isEmpty 全覆盖，重复值只删第一个</t>
+          <t>补位（组员5 未写）：五个实现结论一致；reverse2(null) 返回 null，栈版本对 null 抛 IAE</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>LZ78</t>
+          <t>Palindrome</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -625,14 +625,14 @@
       </c>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>compress/decompress 往返；尾部重复短语会追加 END_OF_STREAM token</t>
+          <t>补位（组员5 未写）：类为包级私有；三个实现结论一致；null、空串、单字符都算回文</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>DamerauLevenshteinDistance</t>
+          <t>CountWords</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>null 输入抛 IAE；相邻换位按 1 次编辑计</t>
+          <t>补位（组员5 未写）：只含空格或特殊字符时返回 1 而不是 0（trim+split 的缺陷，已按实际行为断言）</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>BitRotate</t>
+          <t>LongestCommonPrefix</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -696,11 +696,11 @@
         <v>6</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>私有构造器抛 UOE；shift 按 32 取模；行覆盖 85.7% 是构造器那句 throw 没走到</t>
+          <t>补位（组员5 未写）：会就地排序入参数组；null / 空数组返回空串</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>PermutationCipher</t>
+          <t>InsertionSort</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -727,14 +727,14 @@
       </c>
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>解密无条件删末尾 X，明文本身以 X 结尾会被吃掉（源码缺陷，已按实际行为断言）</t>
+          <t>补位（组员5 未写）：包级类；sort(array,start,end) 只排子区间；sentinelSort(null) 返回 null</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>StackOfLinkedList</t>
+          <t>BubbleSort</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -761,60 +761,264 @@
       </c>
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>包级类，测试同包实例化；泛型排序，测了 Integer 与 String</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>SortedLinkedList</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>姚圣宇</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="2">
+        <f>IF(OR(E9="",F9=""),"",ROUND((F9-E9)*1440,0))</f>
+        <v/>
+      </c>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>有序链表；insert/delete/search/isEmpty 全覆盖，重复值只删第一个</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>LZ78</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>姚圣宇</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="2">
+        <f>IF(OR(E10="",F10=""),"",ROUND((F10-E10)*1440,0))</f>
+        <v/>
+      </c>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>compress/decompress 往返；尾部重复短语会追加 END_OF_STREAM token</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>DamerauLevenshteinDistance</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>姚圣宇</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="2">
+        <f>IF(OR(E11="",F11=""),"",ROUND((F11-E11)*1440,0))</f>
+        <v/>
+      </c>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>null 输入抛 IAE；相邻换位按 1 次编辑计</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>BitRotate</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>姚圣宇</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="2">
+        <f>IF(OR(E12="",F12=""),"",ROUND((F12-E12)*1440,0))</f>
+        <v/>
+      </c>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>私有构造器抛 UOE；shift 按 32 取模；行覆盖 85.7% 是构造器那句 throw 没走到</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>PermutationCipher</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>姚圣宇</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="2">
+        <f>IF(OR(E13="",F13=""),"",ROUND((F13-E13)*1440,0))</f>
+        <v/>
+      </c>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>解密无条件删末尾 X，明文本身以 X 结尾会被吃掉（源码缺陷，已按实际行为断言）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>StackOfLinkedList</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>姚圣宇</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="2">
+        <f>IF(OR(E14="",F14=""),"",ROUND((F14-E14)*1440,0))</f>
+        <v/>
+      </c>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>清单类名 StackOfLinkedList，实际可实例化的类是同文件的 LinkedListStack；空栈 toString 抛 SIOOBE</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>7 个案例</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6">
-        <f>SUM(G2:G8)</f>
-        <v/>
-      </c>
-      <c r="H9" s="6">
-        <f>SUM(H2:H8)</f>
-        <v/>
-      </c>
-      <c r="I9" s="6">
-        <f>SUM(I2:I8)</f>
-        <v/>
-      </c>
-      <c r="J9" s="6">
-        <f>SUM(J2:J8)</f>
-        <v/>
-      </c>
-      <c r="K9" s="6" t="n"/>
-    </row>
-    <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>说明：清单第 14–26 行归组员6，其中 15–20（DeterminantOfMatrix / ExtendedEuclideanAlgorithm / MedianOfRunningArray / QuadraticEquationSolver / SumOfDigits / JumpSearch）组员5 已在同一包下提交同名测试，无法重复，故本表只列 7 个实际可交付的案例。日期/开始/结束/查资料 由本人按实际计时填写。</t>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>13 个案例</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6">
+        <f>SUM(G2:G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="6">
+        <f>SUM(H2:H14)</f>
+        <v/>
+      </c>
+      <c r="I15" s="6">
+        <f>SUM(I2:I14)</f>
+        <v/>
+      </c>
+      <c r="J15" s="6">
+        <f>SUM(J2:J14)</f>
+        <v/>
+      </c>
+      <c r="K15" s="6" t="n"/>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>说明：13 个案例 = 清单第 14–26 行中未被组员5 占用的 7 个（BubbleSort、SortedLinkedList、LZ78、DamerauLevenshteinDistance、BitRotate、PermutationCipher、StackOfLinkedList）+ 补位的 6 个（LinearSearch、ReverseString、Palindrome、CountWords、LongestCommonPrefix、InsertionSort，组员5 认领但未写）。清单第 15–20 行已由组员5 在同一包下提交同名测试，无法重复。日期/开始/结束/查资料 由本人按实际计时填写。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A17:K17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -826,7 +1030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -872,19 +1076,19 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>BubbleSort</t>
+          <t>LinearSearch</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>com.thealgorithms.sorts.BubbleSort</t>
+          <t>com.thealgorithms.searches.LinearSearch</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v>6</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -900,47 +1104,47 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>SortedLinkedList</t>
+          <t>ReverseString</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>com.thealgorithms.datastructures.lists.SortedLinkedList</t>
+          <t>com.thealgorithms.strings.ReverseString</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>LZ78</t>
+          <t>Palindrome</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>com.thealgorithms.compression.LZ78</t>
+          <t>com.thealgorithms.strings.Palindrome</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -956,12 +1160,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DamerauLevenshteinDistance</t>
+          <t>CountWords</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>com.thealgorithms.dynamicprogramming.DamerauLevenshteinDistance</t>
+          <t>com.thealgorithms.strings.CountWords</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -984,51 +1188,51 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>BitRotate</t>
+          <t>LongestCommonPrefix</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>com.thealgorithms.bitmanipulation.BitRotate</t>
+          <t>com.thealgorithms.strings.LongestCommonPrefix</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v>6</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>PermutationCipher</t>
+          <t>InsertionSort</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>com.thealgorithms.ciphers.PermutationCipher</t>
+          <t>com.thealgorithms.sorts.InsertionSort</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1040,26 +1244,194 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>BubbleSort</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>com.thealgorithms.sorts.BubbleSort</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>SortedLinkedList</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>com.thealgorithms.datastructures.lists.SortedLinkedList</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>96.3%</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>85.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>LZ78</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>com.thealgorithms.compression.LZ78</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>DamerauLevenshteinDistance</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>com.thealgorithms.dynamicprogramming.DamerauLevenshteinDistance</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>BitRotate</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>com.thealgorithms.bitmanipulation.BitRotate</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>PermutationCipher</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>com.thealgorithms.ciphers.PermutationCipher</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>96.4%</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>StackOfLinkedList</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>com.thealgorithms.datastructures.stacks.LinkedListStack</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C14" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D14" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
